--- a/src/assets/employees/faten.xlsx
+++ b/src/assets/employees/faten.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F9"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -559,9 +559,29 @@
         <v>2026-09-07</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>faten</v>
+      </c>
+      <c r="B9" t="str">
+        <v>achat</v>
+      </c>
+      <c r="C9" t="str">
+        <v>additive clc_clsb</v>
+      </c>
+      <c r="D9" t="str">
+        <v>etude des signaux programme LACTA CLC</v>
+      </c>
+      <c r="E9">
+        <v>3</v>
+      </c>
+      <c r="F9" t="str">
+        <v>2026-09-09</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F9"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/src/assets/employees/faten.xlsx
+++ b/src/assets/employees/faten.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F8"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -527,16 +527,16 @@
         <v>achat</v>
       </c>
       <c r="C7" t="str">
-        <v>sonede</v>
+        <v>sms2i</v>
       </c>
       <c r="D7" t="str">
-        <v>suivi bc sonede</v>
+        <v>Agilité drive + Trello + Daily metting</v>
       </c>
       <c r="E7">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F7" t="str">
-        <v>2026-09-07</v>
+        <v>2026-09-11</v>
       </c>
     </row>
     <row r="8">
@@ -550,38 +550,18 @@
         <v>sms2i</v>
       </c>
       <c r="D8" t="str">
-        <v>suivi camion</v>
+        <v>congé</v>
       </c>
       <c r="E8">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="F8" t="str">
-        <v>2026-09-07</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>faten</v>
-      </c>
-      <c r="B9" t="str">
-        <v>achat</v>
-      </c>
-      <c r="C9" t="str">
-        <v>additive clc_clsb</v>
-      </c>
-      <c r="D9" t="str">
-        <v>etude des signaux programme LACTA CLC</v>
-      </c>
-      <c r="E9">
-        <v>3</v>
-      </c>
-      <c r="F9" t="str">
-        <v>2026-09-09</v>
+        <v>2026-09-11</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F8"/>
   </ignoredErrors>
 </worksheet>
 </file>